--- a/光伏配储项目/电价数据/2026/素善站.xlsx
+++ b/光伏配储项目/电价数据/2026/素善站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34671</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.87661</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0757</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.80332</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.7286699999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17346</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25473</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6831699999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59329</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.76737</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12671</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44278</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67732</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89471</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21229</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.46118</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.05552</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05208</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31595</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.36001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.71917</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.77428</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.3126</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.7688700000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9496599999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7935399999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7661699999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50452</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.79723</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.97975</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.09366</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5708300000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5911900000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.58028</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5808099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.43653</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.5343300000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66976</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9127799999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.91261</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.7565499999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42591</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7242799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.28863</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6901499999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.07244</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.32997</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.47693</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.24745</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04996</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.41724</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.22789</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.45964</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.05554</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.21253</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.91228</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.13779</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.05937</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05462</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90927</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.16632</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.00601</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.48144</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.92203</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9787100000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47854</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33839</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.57433</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.54614</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.55929</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.49551</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.41709</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.47639</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.53707</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.16395</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20154</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.12333</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.91126</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7372300000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.72482</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.95739</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.95499</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.99688</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.95573</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.11457</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78901</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7991699999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.81604</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.07084</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.59888</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.98898</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.95016</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7696499999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8614299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.08553</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.62714</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43371</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51416</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5400199999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.71262</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.76436</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7124199999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.68423</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70229</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52676</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.68187</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.92835</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81659</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.24573</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48955</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.65427</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8393999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.03638</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.69639</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.28496</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.89883</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6459199999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57668</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7169099999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.48407</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34646</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.56057</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.53725</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.47277</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.48699</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.86122</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47861</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7614500000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.47656</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.67884</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.51412</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.47503</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.72161</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.15932</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8347899999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.74049</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5708300000000001</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.43159</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.61321</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.71812</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9241</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6472100000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66362</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6874400000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.66106</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5624600000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.52658</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3971</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14322</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02354</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.56513</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23645</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18845</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.42851</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.23821</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21229</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18992</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17096</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19819</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.08506</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03274000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20601</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06016</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05836</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31535</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.62671</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.47225</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5306900000000001</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.79253</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8703</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5716599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.52058</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.44784</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.49051</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.68063</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70239</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.10954</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.54113</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.72093</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7307100000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5774600000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32292</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.83666</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.4876</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.49641</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.67564</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.46687</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.55664</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.46508</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.50615</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.50834</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5686</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.61019</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.47898</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.67175</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.53784</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.49805</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5409700000000001</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5380900000000001</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.4992200000000001</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.49161</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.48929</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.49362</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.51139</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.49257</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.56186</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.68114</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.53025</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.6716599999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.52408</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.6209600000000001</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.55489</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.53938</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.52887</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.26319</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.15492</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.73855</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.07938</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.85362</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.97773</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.1443</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.8911699999999999</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.8585199999999999</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.70772</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.56936</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.6265700000000001</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.7155900000000001</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.88975</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.58385</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.7408899999999999</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.62795</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.58592</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.48412</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.22936</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.52671</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.48603</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.47131</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.47742</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.47306</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.45208</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.53446</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.62875</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.96223</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.50975</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.62022</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.49886</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.38869</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.25152</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18373</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.21098</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.24798</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24694</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.21871</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.22647</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27778</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27964</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3023</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1345</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.68341</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48516</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50829</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.56775</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.73314</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.49544</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.55488</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.46271</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68492</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46908</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47607</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72417</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23892</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.21367</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19184</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18437</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27178</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27244</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18324</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.23149</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19537</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15823</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14998</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.21315</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23571</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25484</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.28385</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28466</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.22683</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.17469</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31855</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.03405</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.61378</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5254</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29447</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60433</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80137</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49498</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44442</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3121</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.52618</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57208</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67725</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.80545</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.72224</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5814600000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64112</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30872</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.25731</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.02052</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.50446</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41415</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.23855</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.2436</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.23957</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.26435</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.19433</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.19742</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.23244</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21485</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15796</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.02198</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.02412</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.02344</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15821</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.03567</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19296</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15699</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14801</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15234</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18895</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15009</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15269</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15529</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.02358</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15789</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.02366</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16832</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17526</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26185</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.12275</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25504</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10725</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00154</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21179</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.23119</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25387</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25054</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.17577</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18254</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25399</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16585</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.17027</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.24574</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.02655</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17764</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17477</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.03746</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21631</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20758</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.03521</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.03536</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.03536</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.03527</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18875</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.03536</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.03536</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16594</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02842</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009089999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16617</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01289</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03454</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00368</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03466</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21268</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.03468</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26339</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.02553</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15541</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15526</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15281</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14907</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13866</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.03287</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.03215</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.03104</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41276</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.17814</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.26435</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85577</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8626900000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08799</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.03335</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.58116</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47553</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6280399999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.76522</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9341900000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.59545</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7969700000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7952</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.79925</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.89312</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30269</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25454</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17608</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24637</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24009</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19136</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15368</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18713</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.14852</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14119</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16754</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21987</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23014</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23869</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25873</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28643</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5668800000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46955</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.15335</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.80003</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7973300000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5333600000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.66144</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.84405</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.52311</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19715</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31266</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48781</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.49197</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.96799</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.77855</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5243099999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6534099999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45733</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53584</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.48778</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6311100000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.59494</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.92077</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.81513</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.70272</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.57962</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31729</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5336900000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19786</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.51022</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5609299999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32098</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6920499999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4669700000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.47927</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.47097</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.50815</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.48606</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44129</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3358</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19871</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04815</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12192</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18725</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16311</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15751</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.63624</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.46642</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53486</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5834199999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.50593</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.48066</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49537</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36632</v>
       </c>
     </row>
   </sheetData>
